--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110638385</v>
       </c>
       <c r="B2" t="n">
-        <v>77515</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552967.3647888975</v>
+        <v>552967</v>
       </c>
       <c r="R2" t="n">
-        <v>6830463.108037909</v>
+        <v>6830463</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +759,9 @@
           <t>2023-07-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,12 +792,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -817,7 +807,7 @@
         <v>110637827</v>
       </c>
       <c r="B3" t="n">
-        <v>96368</v>
+        <v>98391</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -874,10 +864,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552901.7060830347</v>
+        <v>552901</v>
       </c>
       <c r="R3" t="n">
-        <v>6830517.312678093</v>
+        <v>6830518</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,19 +897,9 @@
           <t>2023-07-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -950,12 +930,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -965,7 +945,7 @@
         <v>110638014</v>
       </c>
       <c r="B4" t="n">
-        <v>78578</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,10 +993,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552941.6134135833</v>
+        <v>552941</v>
       </c>
       <c r="R4" t="n">
-        <v>6830526.015056835</v>
+        <v>6830526</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1046,19 +1026,9 @@
           <t>2023-07-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1089,12 +1059,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1104,7 +1074,7 @@
         <v>110638118</v>
       </c>
       <c r="B5" t="n">
-        <v>93057</v>
+        <v>94771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1153,10 +1123,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552956.773359548</v>
+        <v>552957</v>
       </c>
       <c r="R5" t="n">
-        <v>6830501.022033119</v>
+        <v>6830501</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1186,19 +1156,9 @@
           <t>2023-07-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1229,12 +1189,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1244,7 +1204,7 @@
         <v>110743711</v>
       </c>
       <c r="B6" t="n">
-        <v>77515</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1292,10 +1252,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552892.5547006417</v>
+        <v>552893</v>
       </c>
       <c r="R6" t="n">
-        <v>6830430.072787996</v>
+        <v>6830430</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1325,19 +1285,9 @@
           <t>2023-07-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1368,12 +1318,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1383,7 +1333,7 @@
         <v>111193955</v>
       </c>
       <c r="B7" t="n">
-        <v>78536</v>
+        <v>79812</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1423,10 +1373,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553023.5105378892</v>
+        <v>553024</v>
       </c>
       <c r="R7" t="n">
-        <v>6830438.743373218</v>
+        <v>6830439</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1456,19 +1406,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1499,12 +1439,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1514,7 +1454,7 @@
         <v>111192993</v>
       </c>
       <c r="B8" t="n">
-        <v>89423</v>
+        <v>90975</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1562,10 +1502,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553071.9000553357</v>
+        <v>553072</v>
       </c>
       <c r="R8" t="n">
-        <v>6830267.660229918</v>
+        <v>6830267</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1595,19 +1535,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1633,12 +1563,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1648,7 +1578,7 @@
         <v>111192740</v>
       </c>
       <c r="B9" t="n">
-        <v>77515</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1688,10 +1618,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553072.0096877192</v>
+        <v>553072</v>
       </c>
       <c r="R9" t="n">
-        <v>6830260.522142665</v>
+        <v>6830260</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1721,19 +1651,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1759,12 +1679,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1774,7 +1694,7 @@
         <v>111193576</v>
       </c>
       <c r="B10" t="n">
-        <v>77515</v>
+        <v>78771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1814,10 +1734,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553128.9401006458</v>
+        <v>553129</v>
       </c>
       <c r="R10" t="n">
-        <v>6830340.409667426</v>
+        <v>6830340</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1847,19 +1767,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1885,12 +1795,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1900,7 +1810,7 @@
         <v>111193922</v>
       </c>
       <c r="B11" t="n">
-        <v>78579</v>
+        <v>79853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1940,10 +1850,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553023.5105378892</v>
+        <v>553024</v>
       </c>
       <c r="R11" t="n">
-        <v>6830438.743373218</v>
+        <v>6830439</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1973,19 +1883,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2016,12 +1916,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2031,7 +1931,7 @@
         <v>111193383</v>
       </c>
       <c r="B12" t="n">
-        <v>77515</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2071,10 +1971,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553096.7781786197</v>
+        <v>553097</v>
       </c>
       <c r="R12" t="n">
-        <v>6830261.854615855</v>
+        <v>6830262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2104,19 +2004,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2142,12 +2032,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2157,7 +2047,7 @@
         <v>111193851</v>
       </c>
       <c r="B13" t="n">
-        <v>78578</v>
+        <v>79852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2197,10 +2087,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553023.5105378892</v>
+        <v>553024</v>
       </c>
       <c r="R13" t="n">
-        <v>6830438.743373218</v>
+        <v>6830439</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2230,19 +2120,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2273,12 +2153,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2288,7 +2168,7 @@
         <v>111195248</v>
       </c>
       <c r="B14" t="n">
-        <v>77515</v>
+        <v>78771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2328,10 +2208,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553129.8640080557</v>
+        <v>553130</v>
       </c>
       <c r="R14" t="n">
-        <v>6830342.327770936</v>
+        <v>6830342</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2361,19 +2241,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2399,7 +2269,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2414,7 +2284,7 @@
         <v>111195897</v>
       </c>
       <c r="B15" t="n">
-        <v>78605</v>
+        <v>79881</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2454,10 +2324,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553082.9568298531</v>
+        <v>553083</v>
       </c>
       <c r="R15" t="n">
-        <v>6830261.642265202</v>
+        <v>6830262</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2487,19 +2357,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2530,7 +2390,7 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110638385</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,12 +792,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -807,7 +807,7 @@
         <v>110637827</v>
       </c>
       <c r="B3" t="n">
-        <v>98391</v>
+        <v>98397</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -945,7 +945,7 @@
         <v>110638014</v>
       </c>
       <c r="B4" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1059,12 +1059,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
         <v>110638118</v>
       </c>
       <c r="B5" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1189,12 +1189,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>110743711</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
         <v>111193955</v>
       </c>
       <c r="B7" t="n">
-        <v>79812</v>
+        <v>79813</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>111192993</v>
       </c>
       <c r="B8" t="n">
-        <v>90975</v>
+        <v>90981</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1563,12 +1563,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Jens Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
         <v>111192740</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1679,12 +1679,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Jens Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1694,7 +1694,7 @@
         <v>111193576</v>
       </c>
       <c r="B10" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1795,12 +1795,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Jens Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1810,7 +1810,7 @@
         <v>111193922</v>
       </c>
       <c r="B11" t="n">
-        <v>79853</v>
+        <v>79854</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1916,12 +1916,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Jens Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
         <v>111193383</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2032,12 +2032,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
         <v>111193851</v>
       </c>
       <c r="B13" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2153,12 +2153,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Jens Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2168,7 +2168,7 @@
         <v>111195248</v>
       </c>
       <c r="B14" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2284,7 +2284,7 @@
         <v>111195897</v>
       </c>
       <c r="B15" t="n">
-        <v>79881</v>
+        <v>79882</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110638385</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>110637827</v>
       </c>
       <c r="B3" t="n">
-        <v>98397</v>
+        <v>98400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>110638014</v>
       </c>
       <c r="B4" t="n">
-        <v>79853</v>
+        <v>79856</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>110638118</v>
       </c>
       <c r="B5" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>110743711</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>111193955</v>
       </c>
       <c r="B7" t="n">
-        <v>79813</v>
+        <v>79816</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>111192993</v>
       </c>
       <c r="B8" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jens Hansen, Carina Frost</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
         <v>111192740</v>
       </c>
       <c r="B9" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jens Hansen, Carina Frost</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1694,7 +1694,7 @@
         <v>111193576</v>
       </c>
       <c r="B10" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jens Hansen, Carina Frost</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1810,7 +1810,7 @@
         <v>111193922</v>
       </c>
       <c r="B11" t="n">
-        <v>79854</v>
+        <v>79857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jens Hansen, Carina Frost</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
         <v>111193383</v>
       </c>
       <c r="B12" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>111193851</v>
       </c>
       <c r="B13" t="n">
-        <v>79853</v>
+        <v>79856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jens Hansen, Carina Frost</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2168,7 +2168,7 @@
         <v>111195248</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>111195897</v>
       </c>
       <c r="B15" t="n">
-        <v>79882</v>
+        <v>79885</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110638385</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>110637827</v>
       </c>
       <c r="B3" t="n">
-        <v>98400</v>
+        <v>98417</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>110638014</v>
       </c>
       <c r="B4" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>110638118</v>
       </c>
       <c r="B5" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>110743711</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>111193955</v>
       </c>
       <c r="B7" t="n">
-        <v>79816</v>
+        <v>79822</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>111192993</v>
       </c>
       <c r="B8" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>111192740</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>111193576</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>111193922</v>
       </c>
       <c r="B11" t="n">
-        <v>79857</v>
+        <v>79863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>111193383</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>111193851</v>
       </c>
       <c r="B13" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>111195248</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>111195897</v>
       </c>
       <c r="B15" t="n">
-        <v>79885</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110638385</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>110637827</v>
       </c>
       <c r="B3" t="n">
-        <v>98417</v>
+        <v>98523</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>110638014</v>
       </c>
       <c r="B4" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>110638118</v>
       </c>
       <c r="B5" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>110743711</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>111193955</v>
       </c>
       <c r="B7" t="n">
-        <v>79822</v>
+        <v>79827</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>111192993</v>
       </c>
       <c r="B8" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>111192740</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>111193576</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>111193922</v>
       </c>
       <c r="B11" t="n">
-        <v>79863</v>
+        <v>79868</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>111193383</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>111193851</v>
       </c>
       <c r="B13" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>111195248</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>111195897</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>79896</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110638385</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>110637827</v>
       </c>
       <c r="B3" t="n">
-        <v>98523</v>
+        <v>98525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>110638014</v>
       </c>
       <c r="B4" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>110638118</v>
       </c>
       <c r="B5" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>110743711</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>111193955</v>
       </c>
       <c r="B7" t="n">
-        <v>79827</v>
+        <v>79829</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>111192993</v>
       </c>
       <c r="B8" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>111192740</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>111193576</v>
       </c>
       <c r="B10" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>111193922</v>
       </c>
       <c r="B11" t="n">
-        <v>79868</v>
+        <v>79870</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>111193383</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>111193851</v>
       </c>
       <c r="B13" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>111195248</v>
       </c>
       <c r="B14" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>111195897</v>
       </c>
       <c r="B15" t="n">
-        <v>79896</v>
+        <v>79898</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -807,7 +807,7 @@
         <v>110637827</v>
       </c>
       <c r="B3" t="n">
-        <v>98525</v>
+        <v>98100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
         <v>110638118</v>
       </c>
       <c r="B5" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jens Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jens Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 27315-2023 artfynd.xlsx
+++ b/artfynd/A 27315-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
